--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6973,6 +6973,931 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130072210</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>440270</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6796231</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130072226</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>440262</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6796328</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie om 40 m</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130072215</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56313</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>440306</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6796252</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130072209</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91644</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>440272</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6796233</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130072212</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>440217</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6796324</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130072228</v>
+      </c>
+      <c r="B69" t="n">
+        <v>89022</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>510</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>440275</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6796330</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Växer på död stående gran</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130072227</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>440267</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6796355</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130072225</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>440331</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6796205</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 40 m</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130072211</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Södra Snipdalsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>440232</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6796283</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130058892</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,42 +772,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130058851</v>
+        <v>130058920</v>
       </c>
       <c r="B3" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440299</v>
+        <v>440320</v>
       </c>
       <c r="R3" t="n">
-        <v>6796116</v>
+        <v>6796217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,12 +848,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130058865</v>
+        <v>130058897</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440423</v>
+        <v>440385</v>
       </c>
       <c r="R4" t="n">
-        <v>6795897</v>
+        <v>6795928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058873</v>
+        <v>130058901</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,42 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440421</v>
+        <v>440563</v>
       </c>
       <c r="R5" t="n">
-        <v>6795811</v>
+        <v>6795633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130058920</v>
+        <v>130058924</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440320</v>
+        <v>440427</v>
       </c>
       <c r="R6" t="n">
-        <v>6796217</v>
+        <v>6795826</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130058924</v>
+        <v>130058865</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,26 +1184,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1231,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440427</v>
+        <v>440423</v>
       </c>
       <c r="R7" t="n">
-        <v>6795826</v>
+        <v>6795897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1260,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1294,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130058897</v>
+        <v>130058873</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,34 +1289,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440385</v>
+        <v>440421</v>
       </c>
       <c r="R8" t="n">
-        <v>6795928</v>
+        <v>6795811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,45 +1383,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130058901</v>
+        <v>130058851</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440563</v>
+        <v>440299</v>
       </c>
       <c r="R9" t="n">
-        <v>6795633</v>
+        <v>6796116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058859</v>
+        <v>130058913</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,42 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440546</v>
+        <v>440435</v>
       </c>
       <c r="R10" t="n">
-        <v>6795516</v>
+        <v>6795906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130058916</v>
+        <v>130058900</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440367</v>
+        <v>440509</v>
       </c>
       <c r="R11" t="n">
-        <v>6796072</v>
+        <v>6795712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058913</v>
+        <v>130058916</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440435</v>
+        <v>440367</v>
       </c>
       <c r="R12" t="n">
-        <v>6795906</v>
+        <v>6796072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058900</v>
+        <v>130058870</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1790,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440509</v>
+        <v>440554</v>
       </c>
       <c r="R13" t="n">
-        <v>6795712</v>
+        <v>6795518</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130058870</v>
+        <v>130058852</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440554</v>
+        <v>440293</v>
       </c>
       <c r="R14" t="n">
-        <v>6795518</v>
+        <v>6796131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,32 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130058852</v>
+        <v>130058859</v>
       </c>
       <c r="B15" t="n">
-        <v>56930</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440293</v>
+        <v>440546</v>
       </c>
       <c r="R15" t="n">
-        <v>6796131</v>
+        <v>6795516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
         <v>130058915</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>130058912</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>130058923</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058917</v>
+        <v>130058907</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440327</v>
+        <v>440539</v>
       </c>
       <c r="R21" t="n">
-        <v>6796066</v>
+        <v>6795530</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130058907</v>
+        <v>130058914</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440539</v>
+        <v>440428</v>
       </c>
       <c r="R22" t="n">
-        <v>6795530</v>
+        <v>6795921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,54 +2789,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130058885</v>
+        <v>130058917</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440403</v>
+        <v>440327</v>
       </c>
       <c r="R23" t="n">
-        <v>6795911</v>
+        <v>6796066</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,7 +2868,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2889,7 @@
         <v>130058890</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,45 +2983,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130058914</v>
+        <v>130058839</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440428</v>
+        <v>440390</v>
       </c>
       <c r="R25" t="n">
-        <v>6795921</v>
+        <v>6796019</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3072,6 +3065,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130058839</v>
+        <v>130058885</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,26 +3095,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440390</v>
+        <v>440403</v>
       </c>
       <c r="R26" t="n">
-        <v>6796019</v>
+        <v>6795911</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058863</v>
+        <v>130058911</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,42 +3307,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440340</v>
+        <v>440471</v>
       </c>
       <c r="R28" t="n">
-        <v>6796151</v>
+        <v>6795703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058911</v>
+        <v>130058902</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,16 +3422,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440471</v>
+        <v>440578</v>
       </c>
       <c r="R29" t="n">
-        <v>6795703</v>
+        <v>6795586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,6 +3475,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058902</v>
+        <v>130058863</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,26 +3505,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3536,10 +3537,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440578</v>
+        <v>440340</v>
       </c>
       <c r="R30" t="n">
-        <v>6795586</v>
+        <v>6796151</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3580,7 +3581,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130058899</v>
+        <v>130058906</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440423</v>
+        <v>440552</v>
       </c>
       <c r="R31" t="n">
-        <v>6795866</v>
+        <v>6795519</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130058906</v>
+        <v>130058899</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440552</v>
+        <v>440423</v>
       </c>
       <c r="R32" t="n">
-        <v>6795519</v>
+        <v>6795866</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
         <v>130058898</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>130058910</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>130058860</v>
       </c>
       <c r="B40" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130058871</v>
+        <v>130058904</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4638,42 +4638,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440498</v>
+        <v>440579</v>
       </c>
       <c r="R41" t="n">
-        <v>6795631</v>
+        <v>6795539</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4732,41 +4724,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130058886</v>
+        <v>130058871</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4776,10 +4767,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440577</v>
+        <v>440498</v>
       </c>
       <c r="R42" t="n">
-        <v>6795496</v>
+        <v>6795631</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4811,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4944,45 +4934,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130058904</v>
+        <v>130058886</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440579</v>
+        <v>440577</v>
       </c>
       <c r="R44" t="n">
-        <v>6795539</v>
+        <v>6795496</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5023,6 +5022,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>130058896</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>130058891</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130058876</v>
+        <v>130058842</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,16 +5353,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440393</v>
+        <v>440461</v>
       </c>
       <c r="R48" t="n">
-        <v>6796027</v>
+        <v>6795771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,32 +5447,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130058847</v>
+        <v>130058876</v>
       </c>
       <c r="B49" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440505</v>
+        <v>440393</v>
       </c>
       <c r="R49" t="n">
-        <v>6795644</v>
+        <v>6796027</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,32 +5552,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130058842</v>
+        <v>130058847</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>56930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5585,7 +5585,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440461</v>
+        <v>440505</v>
       </c>
       <c r="R50" t="n">
-        <v>6795771</v>
+        <v>6795644</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130058841</v>
+        <v>130058895</v>
       </c>
       <c r="B51" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5668,34 +5668,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440600</v>
+        <v>440378</v>
       </c>
       <c r="R51" t="n">
-        <v>6795536</v>
+        <v>6795976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5730,12 +5733,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5757,7 +5766,7 @@
         <v>130058909</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5851,10 +5860,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130058895</v>
+        <v>130058841</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5862,37 +5871,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440378</v>
+        <v>440600</v>
       </c>
       <c r="R53" t="n">
-        <v>6795976</v>
+        <v>6795536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5927,18 +5933,12 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5957,53 +5957,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130058855</v>
+        <v>130058908</v>
       </c>
       <c r="B54" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440292</v>
+        <v>440536</v>
       </c>
       <c r="R54" t="n">
-        <v>6796168</v>
+        <v>6795557</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6167,10 +6159,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130058881</v>
+        <v>130058855</v>
       </c>
       <c r="B56" t="n">
-        <v>97669</v>
+        <v>56930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6178,34 +6170,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440433</v>
+        <v>440292</v>
       </c>
       <c r="R56" t="n">
-        <v>6795823</v>
+        <v>6796168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,32 +6264,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130058908</v>
+        <v>130058881</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440536</v>
+        <v>440433</v>
       </c>
       <c r="R57" t="n">
-        <v>6795557</v>
+        <v>6795823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6361,45 +6361,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130058903</v>
+        <v>130058862</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>92917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440589</v>
+        <v>440483</v>
       </c>
       <c r="R58" t="n">
-        <v>6795581</v>
+        <v>6795705</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6440,6 +6447,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6458,10 +6466,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130058867</v>
+        <v>130058903</v>
       </c>
       <c r="B59" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6469,42 +6477,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440564</v>
+        <v>440589</v>
       </c>
       <c r="R59" t="n">
-        <v>6795624</v>
+        <v>6795581</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6563,53 +6563,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130058857</v>
+        <v>130058922</v>
       </c>
       <c r="B60" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440332</v>
+        <v>440269</v>
       </c>
       <c r="R60" t="n">
-        <v>6796088</v>
+        <v>6796343</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6668,41 +6660,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130058862</v>
+        <v>130058867</v>
       </c>
       <c r="B61" t="n">
-        <v>92900</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6710,10 +6703,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440483</v>
+        <v>440564</v>
       </c>
       <c r="R61" t="n">
-        <v>6795705</v>
+        <v>6795624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6754,7 +6747,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6773,45 +6765,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130058922</v>
+        <v>130058857</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440269</v>
+        <v>440332</v>
       </c>
       <c r="R62" t="n">
-        <v>6796343</v>
+        <v>6796088</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130072215</v>
+        <v>130072209</v>
       </c>
       <c r="B66" t="n">
-        <v>56313</v>
+        <v>91644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,34 +7193,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440306</v>
+        <v>440272</v>
       </c>
       <c r="R66" t="n">
-        <v>6796252</v>
+        <v>6796233</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7261,6 +7268,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7279,10 +7287,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130072209</v>
+        <v>130072215</v>
       </c>
       <c r="B67" t="n">
-        <v>91644</v>
+        <v>56313</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7290,41 +7298,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440272</v>
+        <v>440306</v>
       </c>
       <c r="R67" t="n">
-        <v>6796233</v>
+        <v>6796252</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7365,7 +7366,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130072212</v>
+        <v>130072228</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>89022</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7395,42 +7395,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440217</v>
+        <v>440275</v>
       </c>
       <c r="R68" t="n">
-        <v>6796324</v>
+        <v>6796330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7463,6 +7455,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7489,10 +7486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130072228</v>
+        <v>130072212</v>
       </c>
       <c r="B69" t="n">
-        <v>89022</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7500,34 +7497,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440275</v>
+        <v>440217</v>
       </c>
       <c r="R69" t="n">
-        <v>6796330</v>
+        <v>6796324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7560,11 +7565,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7591,7 +7591,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130072227</v>
+        <v>130072225</v>
       </c>
       <c r="B70" t="n">
         <v>79089</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440267</v>
+        <v>440331</v>
       </c>
       <c r="R70" t="n">
-        <v>6796355</v>
+        <v>6796205</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt inom en radie av 20 m</t>
+          <t>Rikligt inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7693,7 +7693,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130072225</v>
+        <v>130072227</v>
       </c>
       <c r="B71" t="n">
         <v>79089</v>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440331</v>
+        <v>440267</v>
       </c>
       <c r="R71" t="n">
-        <v>6796205</v>
+        <v>6796355</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt inom en radie av 40 m</t>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058916</v>
+        <v>130058859</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,34 +1499,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440367</v>
+        <v>440546</v>
       </c>
       <c r="R10" t="n">
-        <v>6796072</v>
+        <v>6795516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130058913</v>
+        <v>130058870</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,34 +1604,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440435</v>
+        <v>440554</v>
       </c>
       <c r="R11" t="n">
-        <v>6795906</v>
+        <v>6795518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1698,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058900</v>
+        <v>130058916</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1717,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440509</v>
+        <v>440367</v>
       </c>
       <c r="R12" t="n">
-        <v>6795712</v>
+        <v>6796072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058870</v>
+        <v>130058913</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,42 +1806,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440554</v>
+        <v>440435</v>
       </c>
       <c r="R13" t="n">
-        <v>6795518</v>
+        <v>6795906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,53 +1892,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130058852</v>
+        <v>130058900</v>
       </c>
       <c r="B14" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440293</v>
+        <v>440509</v>
       </c>
       <c r="R14" t="n">
-        <v>6796131</v>
+        <v>6795712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,32 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130058859</v>
+        <v>130058852</v>
       </c>
       <c r="B15" t="n">
-        <v>57900</v>
+        <v>56931</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440546</v>
+        <v>440293</v>
       </c>
       <c r="R15" t="n">
-        <v>6795516</v>
+        <v>6796131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130058876</v>
+        <v>130058847</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>56931</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440393</v>
+        <v>440505</v>
       </c>
       <c r="R48" t="n">
-        <v>6796027</v>
+        <v>6795644</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,32 +5447,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130058847</v>
+        <v>130058842</v>
       </c>
       <c r="B49" t="n">
-        <v>56931</v>
+        <v>57741</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440505</v>
+        <v>440461</v>
       </c>
       <c r="R49" t="n">
-        <v>6795644</v>
+        <v>6795771</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130058842</v>
+        <v>130058876</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,16 +5563,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440461</v>
+        <v>440393</v>
       </c>
       <c r="R50" t="n">
-        <v>6795771</v>
+        <v>6796027</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -2401,54 +2401,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130058885</v>
+        <v>130058890</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440403</v>
+        <v>440247</v>
       </c>
       <c r="R19" t="n">
-        <v>6795911</v>
+        <v>6796340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,7 +2480,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2508,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130058890</v>
+        <v>130058912</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2543,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440247</v>
+        <v>440474</v>
       </c>
       <c r="R20" t="n">
-        <v>6796340</v>
+        <v>6795761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2595,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058912</v>
+        <v>130058923</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2640,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440474</v>
+        <v>440260</v>
       </c>
       <c r="R21" t="n">
-        <v>6795761</v>
+        <v>6796348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,7 +2692,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130058923</v>
+        <v>130058917</v>
       </c>
       <c r="B22" t="n">
         <v>79095</v>
@@ -2737,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440260</v>
+        <v>440327</v>
       </c>
       <c r="R22" t="n">
-        <v>6796348</v>
+        <v>6796066</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2799,7 +2789,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130058917</v>
+        <v>130058907</v>
       </c>
       <c r="B23" t="n">
         <v>79095</v>
@@ -2834,10 +2824,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440327</v>
+        <v>440539</v>
       </c>
       <c r="R23" t="n">
-        <v>6796066</v>
+        <v>6795530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,7 +2886,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130058907</v>
+        <v>130058914</v>
       </c>
       <c r="B24" t="n">
         <v>79095</v>
@@ -2931,10 +2921,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440539</v>
+        <v>440428</v>
       </c>
       <c r="R24" t="n">
-        <v>6795530</v>
+        <v>6795921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2993,45 +2983,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130058914</v>
+        <v>130058839</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>91603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440428</v>
+        <v>440390</v>
       </c>
       <c r="R25" t="n">
-        <v>6795921</v>
+        <v>6796019</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3072,6 +3065,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130058839</v>
+        <v>130058885</v>
       </c>
       <c r="B26" t="n">
-        <v>91603</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,26 +3095,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440390</v>
+        <v>440403</v>
       </c>
       <c r="R26" t="n">
-        <v>6796019</v>
+        <v>6795911</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3898,53 +3898,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130058882</v>
+        <v>130058898</v>
       </c>
       <c r="B34" t="n">
-        <v>56934</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440465</v>
+        <v>440440</v>
       </c>
       <c r="R34" t="n">
-        <v>6795787</v>
+        <v>6795865</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3977,11 +3969,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Blev skrämd och flög iväg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4008,45 +3995,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130058898</v>
+        <v>130058882</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>56934</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440440</v>
+        <v>440465</v>
       </c>
       <c r="R35" t="n">
-        <v>6795865</v>
+        <v>6795787</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,6 +4074,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Blev skrämd och flög iväg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5957,53 +5957,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130058848</v>
+        <v>130058908</v>
       </c>
       <c r="B54" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440460</v>
+        <v>440536</v>
       </c>
       <c r="R54" t="n">
-        <v>6795780</v>
+        <v>6795557</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6062,45 +6054,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130058908</v>
+        <v>130058855</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440536</v>
+        <v>440292</v>
       </c>
       <c r="R55" t="n">
-        <v>6795557</v>
+        <v>6796168</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,7 +6159,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130058855</v>
+        <v>130058848</v>
       </c>
       <c r="B56" t="n">
         <v>56931</v>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440292</v>
+        <v>440460</v>
       </c>
       <c r="R56" t="n">
-        <v>6796168</v>
+        <v>6795780</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6361,45 +6361,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130058922</v>
+        <v>130058862</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>92933</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440269</v>
+        <v>440483</v>
       </c>
       <c r="R58" t="n">
-        <v>6796343</v>
+        <v>6795705</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6440,6 +6447,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6458,45 +6466,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130058903</v>
+        <v>130058858</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440589</v>
+        <v>440322</v>
       </c>
       <c r="R59" t="n">
-        <v>6795581</v>
+        <v>6796186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6555,32 +6571,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130058867</v>
+        <v>130058857</v>
       </c>
       <c r="B60" t="n">
-        <v>57738</v>
+        <v>56931</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6588,7 +6604,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6598,10 +6614,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440564</v>
+        <v>440332</v>
       </c>
       <c r="R60" t="n">
-        <v>6795624</v>
+        <v>6796088</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6660,41 +6676,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130058862</v>
+        <v>130058867</v>
       </c>
       <c r="B61" t="n">
-        <v>92933</v>
+        <v>57738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6702,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440483</v>
+        <v>440564</v>
       </c>
       <c r="R61" t="n">
-        <v>6795705</v>
+        <v>6795624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6746,7 +6763,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6765,53 +6781,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130058858</v>
+        <v>130058922</v>
       </c>
       <c r="B62" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440322</v>
+        <v>440269</v>
       </c>
       <c r="R62" t="n">
-        <v>6796186</v>
+        <v>6796343</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,53 +6878,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130058857</v>
+        <v>130058903</v>
       </c>
       <c r="B63" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440332</v>
+        <v>440589</v>
       </c>
       <c r="R63" t="n">
-        <v>6796088</v>
+        <v>6795581</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130072212</v>
+        <v>130072228</v>
       </c>
       <c r="B68" t="n">
-        <v>57738</v>
+        <v>89038</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7395,42 +7395,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440217</v>
+        <v>440275</v>
       </c>
       <c r="R68" t="n">
-        <v>6796324</v>
+        <v>6796330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7463,6 +7455,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7489,10 +7486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130072228</v>
+        <v>130072212</v>
       </c>
       <c r="B69" t="n">
-        <v>89038</v>
+        <v>57738</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7500,34 +7497,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440275</v>
+        <v>440217</v>
       </c>
       <c r="R69" t="n">
-        <v>6796330</v>
+        <v>6796324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7560,11 +7565,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130058901</v>
+        <v>130058892</v>
       </c>
       <c r="B2" t="n">
         <v>79095</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440563</v>
+        <v>440299</v>
       </c>
       <c r="R2" t="n">
-        <v>6795633</v>
+        <v>6796242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130058865</v>
+        <v>130058920</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440423</v>
+        <v>440320</v>
       </c>
       <c r="R3" t="n">
-        <v>6795897</v>
+        <v>6796217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,12 +848,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130058873</v>
+        <v>130058924</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,31 +889,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440421</v>
+        <v>440427</v>
       </c>
       <c r="R4" t="n">
-        <v>6795811</v>
+        <v>6795826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058892</v>
+        <v>130058897</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1017,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440299</v>
+        <v>440385</v>
       </c>
       <c r="R5" t="n">
-        <v>6796242</v>
+        <v>6795928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1076,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130058920</v>
+        <v>130058901</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1108,19 +1105,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440320</v>
+        <v>440563</v>
       </c>
       <c r="R6" t="n">
-        <v>6796217</v>
+        <v>6795633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,18 +1149,12 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,37 +1173,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130058924</v>
+        <v>130058851</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1223,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440427</v>
+        <v>440299</v>
       </c>
       <c r="R7" t="n">
-        <v>6795826</v>
+        <v>6796116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,7 +1260,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1286,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130058897</v>
+        <v>130058865</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,34 +1289,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440385</v>
+        <v>440423</v>
       </c>
       <c r="R8" t="n">
-        <v>6795928</v>
+        <v>6795897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,32 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130058851</v>
+        <v>130058873</v>
       </c>
       <c r="B9" t="n">
-        <v>56931</v>
+        <v>57738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440299</v>
+        <v>440421</v>
       </c>
       <c r="R9" t="n">
-        <v>6796116</v>
+        <v>6795811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058859</v>
+        <v>130058852</v>
       </c>
       <c r="B10" t="n">
-        <v>57900</v>
+        <v>56931</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440546</v>
+        <v>440293</v>
       </c>
       <c r="R10" t="n">
-        <v>6795516</v>
+        <v>6796131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130058870</v>
+        <v>130058916</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,42 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440554</v>
+        <v>440367</v>
       </c>
       <c r="R11" t="n">
-        <v>6795518</v>
+        <v>6796072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1690,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058916</v>
+        <v>130058913</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1733,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440367</v>
+        <v>440435</v>
       </c>
       <c r="R12" t="n">
-        <v>6796072</v>
+        <v>6795906</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058913</v>
+        <v>130058900</v>
       </c>
       <c r="B13" t="n">
         <v>79095</v>
@@ -1830,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440435</v>
+        <v>440509</v>
       </c>
       <c r="R13" t="n">
-        <v>6795906</v>
+        <v>6795712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130058900</v>
+        <v>130058870</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,34 +1895,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440509</v>
+        <v>440554</v>
       </c>
       <c r="R14" t="n">
-        <v>6795712</v>
+        <v>6795518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,32 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130058852</v>
+        <v>130058859</v>
       </c>
       <c r="B15" t="n">
-        <v>56931</v>
+        <v>57900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440293</v>
+        <v>440546</v>
       </c>
       <c r="R15" t="n">
-        <v>6796131</v>
+        <v>6795516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130058890</v>
+        <v>130058912</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440247</v>
+        <v>440474</v>
       </c>
       <c r="R19" t="n">
-        <v>6796340</v>
+        <v>6795761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130058912</v>
+        <v>130058923</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440474</v>
+        <v>440260</v>
       </c>
       <c r="R20" t="n">
-        <v>6795761</v>
+        <v>6796348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058923</v>
+        <v>130058917</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440260</v>
+        <v>440327</v>
       </c>
       <c r="R21" t="n">
-        <v>6796348</v>
+        <v>6796066</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130058917</v>
+        <v>130058907</v>
       </c>
       <c r="B22" t="n">
         <v>79095</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440327</v>
+        <v>440539</v>
       </c>
       <c r="R22" t="n">
-        <v>6796066</v>
+        <v>6795530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130058907</v>
+        <v>130058890</v>
       </c>
       <c r="B23" t="n">
         <v>79095</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440539</v>
+        <v>440247</v>
       </c>
       <c r="R23" t="n">
-        <v>6795530</v>
+        <v>6796340</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
         <v>130058839</v>
       </c>
       <c r="B25" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058863</v>
+        <v>130058911</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,42 +3307,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440340</v>
+        <v>440471</v>
       </c>
       <c r="R28" t="n">
-        <v>6796151</v>
+        <v>6795703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,7 +3393,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058911</v>
+        <v>130058902</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3430,16 +3422,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440471</v>
+        <v>440578</v>
       </c>
       <c r="R29" t="n">
-        <v>6795703</v>
+        <v>6795586</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,6 +3475,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058902</v>
+        <v>130058863</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,26 +3505,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3536,10 +3537,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440578</v>
+        <v>440340</v>
       </c>
       <c r="R30" t="n">
-        <v>6795586</v>
+        <v>6796151</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3580,7 +3581,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4837,45 +4837,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130058904</v>
+        <v>130058886</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440579</v>
+        <v>440577</v>
       </c>
       <c r="R43" t="n">
-        <v>6795539</v>
+        <v>6795496</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4916,6 +4925,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4934,54 +4944,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130058886</v>
+        <v>130058904</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440577</v>
+        <v>440579</v>
       </c>
       <c r="R44" t="n">
-        <v>6795496</v>
+        <v>6795539</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5022,7 +5023,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130058847</v>
+        <v>130058842</v>
       </c>
       <c r="B48" t="n">
-        <v>56931</v>
+        <v>57741</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440505</v>
+        <v>440461</v>
       </c>
       <c r="R48" t="n">
-        <v>6795644</v>
+        <v>6795771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,32 +5447,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130058842</v>
+        <v>130058847</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>56931</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440461</v>
+        <v>440505</v>
       </c>
       <c r="R49" t="n">
-        <v>6795771</v>
+        <v>6795644</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130058841</v>
+        <v>130058909</v>
       </c>
       <c r="B51" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440600</v>
+        <v>440505</v>
       </c>
       <c r="R51" t="n">
-        <v>6795536</v>
+        <v>6795634</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130058909</v>
+        <v>130058895</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -5783,16 +5783,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440505</v>
+        <v>440378</v>
       </c>
       <c r="R52" t="n">
-        <v>6795634</v>
+        <v>6795976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5827,12 +5830,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5851,10 +5860,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130058895</v>
+        <v>130058841</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5862,37 +5871,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440378</v>
+        <v>440600</v>
       </c>
       <c r="R53" t="n">
-        <v>6795976</v>
+        <v>6795536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5927,18 +5933,12 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>130058881</v>
       </c>
       <c r="B57" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130058862</v>
+        <v>130058858</v>
       </c>
       <c r="B58" t="n">
-        <v>92933</v>
+        <v>56931</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6372,30 +6372,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6403,10 +6404,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440483</v>
+        <v>440322</v>
       </c>
       <c r="R58" t="n">
-        <v>6795705</v>
+        <v>6796186</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6447,7 +6448,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130058858</v>
+        <v>130058857</v>
       </c>
       <c r="B59" t="n">
         <v>56931</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440322</v>
+        <v>440332</v>
       </c>
       <c r="R59" t="n">
-        <v>6796186</v>
+        <v>6796088</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130058857</v>
+        <v>130058862</v>
       </c>
       <c r="B60" t="n">
-        <v>56931</v>
+        <v>92935</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,31 +6582,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6614,10 +6613,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440332</v>
+        <v>440483</v>
       </c>
       <c r="R60" t="n">
-        <v>6796088</v>
+        <v>6795705</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6658,6 +6657,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6676,10 +6676,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130058867</v>
+        <v>130058922</v>
       </c>
       <c r="B61" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6687,42 +6687,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440564</v>
+        <v>440269</v>
       </c>
       <c r="R61" t="n">
-        <v>6795624</v>
+        <v>6796343</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6781,7 +6773,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130058922</v>
+        <v>130058903</v>
       </c>
       <c r="B62" t="n">
         <v>79095</v>
@@ -6816,10 +6808,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440269</v>
+        <v>440589</v>
       </c>
       <c r="R62" t="n">
-        <v>6796343</v>
+        <v>6795581</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6878,10 +6870,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130058903</v>
+        <v>130058867</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6889,34 +6881,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440589</v>
+        <v>440564</v>
       </c>
       <c r="R63" t="n">
-        <v>6795581</v>
+        <v>6795624</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7282,7 +7282,7 @@
         <v>130072209</v>
       </c>
       <c r="B67" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130058892</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,37 +772,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130058920</v>
+        <v>130058851</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440320</v>
+        <v>440299</v>
       </c>
       <c r="R3" t="n">
-        <v>6796217</v>
+        <v>6796116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,18 +853,12 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130058924</v>
+        <v>130058865</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,26 +888,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440427</v>
+        <v>440423</v>
       </c>
       <c r="R4" t="n">
-        <v>6795826</v>
+        <v>6795897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058897</v>
+        <v>130058873</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +993,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440385</v>
+        <v>440421</v>
       </c>
       <c r="R5" t="n">
-        <v>6795928</v>
+        <v>6795811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130058901</v>
+        <v>130058920</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,16 +1116,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440563</v>
+        <v>440320</v>
       </c>
       <c r="R6" t="n">
-        <v>6795633</v>
+        <v>6796217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,12 +1163,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,42 +1193,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130058851</v>
+        <v>130058924</v>
       </c>
       <c r="B7" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1216,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440299</v>
+        <v>440427</v>
       </c>
       <c r="R7" t="n">
-        <v>6796116</v>
+        <v>6795826</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,6 +1275,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130058865</v>
+        <v>130058897</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,42 +1305,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440423</v>
+        <v>440385</v>
       </c>
       <c r="R8" t="n">
-        <v>6795897</v>
+        <v>6795928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130058873</v>
+        <v>130058901</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,42 +1402,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440421</v>
+        <v>440563</v>
       </c>
       <c r="R9" t="n">
-        <v>6795811</v>
+        <v>6795633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058852</v>
+        <v>130058859</v>
       </c>
       <c r="B10" t="n">
-        <v>56931</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440293</v>
+        <v>440546</v>
       </c>
       <c r="R10" t="n">
-        <v>6796131</v>
+        <v>6795516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
         <v>130058916</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>130058913</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>130058900</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>130058870</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,32 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130058859</v>
+        <v>130058852</v>
       </c>
       <c r="B15" t="n">
-        <v>57900</v>
+        <v>57016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440546</v>
+        <v>440293</v>
       </c>
       <c r="R15" t="n">
-        <v>6795516</v>
+        <v>6796131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
         <v>130058869</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130058868</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130058915</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130058912</v>
+        <v>130058923</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440474</v>
+        <v>440260</v>
       </c>
       <c r="R19" t="n">
-        <v>6795761</v>
+        <v>6796348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130058923</v>
+        <v>130058917</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440260</v>
+        <v>440327</v>
       </c>
       <c r="R20" t="n">
-        <v>6796348</v>
+        <v>6796066</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058917</v>
+        <v>130058907</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440327</v>
+        <v>440539</v>
       </c>
       <c r="R21" t="n">
-        <v>6796066</v>
+        <v>6795530</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,45 +2692,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130058907</v>
+        <v>130058885</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440539</v>
+        <v>440403</v>
       </c>
       <c r="R22" t="n">
-        <v>6795530</v>
+        <v>6795911</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2771,6 +2780,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2792,7 +2802,7 @@
         <v>130058890</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,7 +2899,7 @@
         <v>130058914</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2986,7 +2996,7 @@
         <v>130058839</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,54 +3094,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130058885</v>
+        <v>130058912</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440403</v>
+        <v>440474</v>
       </c>
       <c r="R26" t="n">
-        <v>6795911</v>
+        <v>6795761</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3172,7 +3173,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>130058850</v>
       </c>
       <c r="B27" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058911</v>
+        <v>130058863</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,34 +3307,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440471</v>
+        <v>440340</v>
       </c>
       <c r="R28" t="n">
-        <v>6795703</v>
+        <v>6796151</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058902</v>
+        <v>130058911</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,19 +3430,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440578</v>
+        <v>440471</v>
       </c>
       <c r="R29" t="n">
-        <v>6795586</v>
+        <v>6795703</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3475,7 +3480,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3498,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058863</v>
+        <v>130058902</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,31 +3509,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3537,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440340</v>
+        <v>440578</v>
       </c>
       <c r="R30" t="n">
-        <v>6796151</v>
+        <v>6795586</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3581,6 +3580,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>130058899</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>130058906</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130058880</v>
+        <v>130058898</v>
       </c>
       <c r="B33" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3804,42 +3804,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440373</v>
+        <v>440440</v>
       </c>
       <c r="R33" t="n">
-        <v>6796078</v>
+        <v>6795865</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3898,10 +3890,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130058898</v>
+        <v>130058880</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,34 +3901,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440440</v>
+        <v>440373</v>
       </c>
       <c r="R34" t="n">
-        <v>6795865</v>
+        <v>6796078</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,7 +3998,7 @@
         <v>130058882</v>
       </c>
       <c r="B35" t="n">
-        <v>56934</v>
+        <v>57019</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>130058910</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>130058872</v>
       </c>
       <c r="B37" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>130058874</v>
       </c>
       <c r="B38" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>130058856</v>
       </c>
       <c r="B39" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>130058860</v>
       </c>
       <c r="B40" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>130058871</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4732,40 +4732,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130058866</v>
+        <v>130058886</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4775,10 +4776,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440489</v>
+        <v>440577</v>
       </c>
       <c r="R42" t="n">
-        <v>6795771</v>
+        <v>6795496</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,6 +4820,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4837,41 +4839,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130058886</v>
+        <v>130058866</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4881,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440577</v>
+        <v>440489</v>
       </c>
       <c r="R43" t="n">
-        <v>6795496</v>
+        <v>6795771</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4925,7 +4926,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>130058904</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>130058896</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>130058891</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130058842</v>
+        <v>130058876</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,16 +5353,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440461</v>
+        <v>440393</v>
       </c>
       <c r="R48" t="n">
-        <v>6795771</v>
+        <v>6796027</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5450,7 +5450,7 @@
         <v>130058847</v>
       </c>
       <c r="B49" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130058876</v>
+        <v>130058842</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,16 +5563,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440393</v>
+        <v>440461</v>
       </c>
       <c r="R50" t="n">
-        <v>6796027</v>
+        <v>6795771</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130058909</v>
+        <v>130058841</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440505</v>
+        <v>440600</v>
       </c>
       <c r="R51" t="n">
-        <v>6795634</v>
+        <v>6795536</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5754,10 +5754,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130058895</v>
+        <v>130058909</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5783,19 +5783,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440378</v>
+        <v>440505</v>
       </c>
       <c r="R52" t="n">
-        <v>6795976</v>
+        <v>6795634</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5830,18 +5827,12 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5860,10 +5851,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130058841</v>
+        <v>130058895</v>
       </c>
       <c r="B53" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5871,34 +5862,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440600</v>
+        <v>440378</v>
       </c>
       <c r="R53" t="n">
-        <v>6795536</v>
+        <v>6795976</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5933,12 +5927,18 @@
           <t>2025-12-09</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5957,45 +5957,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130058908</v>
+        <v>130058855</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440536</v>
+        <v>440292</v>
       </c>
       <c r="R54" t="n">
-        <v>6795557</v>
+        <v>6796168</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,10 +6062,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130058855</v>
+        <v>130058848</v>
       </c>
       <c r="B55" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6097,10 +6105,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440292</v>
+        <v>440460</v>
       </c>
       <c r="R55" t="n">
-        <v>6796168</v>
+        <v>6795780</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,10 +6167,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130058848</v>
+        <v>130058881</v>
       </c>
       <c r="B56" t="n">
-        <v>56931</v>
+        <v>97791</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,42 +6178,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440460</v>
+        <v>440433</v>
       </c>
       <c r="R56" t="n">
-        <v>6795780</v>
+        <v>6795823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,32 +6264,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130058881</v>
+        <v>130058908</v>
       </c>
       <c r="B57" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440433</v>
+        <v>440536</v>
       </c>
       <c r="R57" t="n">
-        <v>6795823</v>
+        <v>6795557</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6361,53 +6361,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130058858</v>
+        <v>130058922</v>
       </c>
       <c r="B58" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440322</v>
+        <v>440269</v>
       </c>
       <c r="R58" t="n">
-        <v>6796186</v>
+        <v>6796343</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6466,10 +6458,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130058857</v>
+        <v>130058858</v>
       </c>
       <c r="B59" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6509,10 +6501,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440332</v>
+        <v>440322</v>
       </c>
       <c r="R59" t="n">
-        <v>6796088</v>
+        <v>6796186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6571,52 +6563,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130058862</v>
+        <v>130058903</v>
       </c>
       <c r="B60" t="n">
-        <v>92935</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440483</v>
+        <v>440589</v>
       </c>
       <c r="R60" t="n">
-        <v>6795705</v>
+        <v>6795581</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6657,7 +6642,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6676,10 +6660,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130058922</v>
+        <v>130058867</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6687,34 +6671,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440269</v>
+        <v>440564</v>
       </c>
       <c r="R61" t="n">
-        <v>6796343</v>
+        <v>6795624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6773,45 +6765,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130058903</v>
+        <v>130058857</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440589</v>
+        <v>440332</v>
       </c>
       <c r="R62" t="n">
-        <v>6795581</v>
+        <v>6796088</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,42 +6870,41 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130058867</v>
+        <v>130058862</v>
       </c>
       <c r="B63" t="n">
-        <v>57738</v>
+        <v>93022</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6913,10 +6912,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440564</v>
+        <v>440483</v>
       </c>
       <c r="R63" t="n">
-        <v>6795624</v>
+        <v>6795705</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6957,6 +6956,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>130072210</v>
       </c>
       <c r="B64" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>130072226</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>130072215</v>
       </c>
       <c r="B66" t="n">
-        <v>56314</v>
+        <v>56399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>130072209</v>
       </c>
       <c r="B67" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130072228</v>
+        <v>130072212</v>
       </c>
       <c r="B68" t="n">
-        <v>89038</v>
+        <v>57823</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7395,34 +7395,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440275</v>
+        <v>440217</v>
       </c>
       <c r="R68" t="n">
-        <v>6796330</v>
+        <v>6796324</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,11 +7463,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7486,10 +7489,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130072212</v>
+        <v>130072228</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>89125</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7497,42 +7500,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440217</v>
+        <v>440275</v>
       </c>
       <c r="R69" t="n">
-        <v>6796324</v>
+        <v>6796330</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7565,6 +7560,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Växer på död stående gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7594,7 +7594,7 @@
         <v>130072211</v>
       </c>
       <c r="B70" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>130072225</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>130072227</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058859</v>
+        <v>130058916</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,42 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440546</v>
+        <v>440367</v>
       </c>
       <c r="R10" t="n">
-        <v>6795516</v>
+        <v>6796072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130058916</v>
+        <v>130058913</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1628,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440367</v>
+        <v>440435</v>
       </c>
       <c r="R11" t="n">
-        <v>6796072</v>
+        <v>6795906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,7 +1682,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058913</v>
+        <v>130058900</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1725,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440435</v>
+        <v>440509</v>
       </c>
       <c r="R12" t="n">
-        <v>6795906</v>
+        <v>6795712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058900</v>
+        <v>130058870</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1790,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440509</v>
+        <v>440554</v>
       </c>
       <c r="R13" t="n">
-        <v>6795712</v>
+        <v>6795518</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130058870</v>
+        <v>130058852</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440554</v>
+        <v>440293</v>
       </c>
       <c r="R14" t="n">
-        <v>6795518</v>
+        <v>6796131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,32 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130058852</v>
+        <v>130058859</v>
       </c>
       <c r="B15" t="n">
-        <v>57016</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440293</v>
+        <v>440546</v>
       </c>
       <c r="R15" t="n">
-        <v>6796131</v>
+        <v>6795516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130058915</v>
+        <v>130058869</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,34 +2105,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440371</v>
+        <v>440599</v>
       </c>
       <c r="R16" t="n">
-        <v>6796052</v>
+        <v>6795514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130058868</v>
+        <v>130058915</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2202,42 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440586</v>
+        <v>440371</v>
       </c>
       <c r="R17" t="n">
-        <v>6795575</v>
+        <v>6796052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130058869</v>
+        <v>130058868</v>
       </c>
       <c r="B18" t="n">
         <v>57823</v>
@@ -2329,7 +2329,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440599</v>
+        <v>440586</v>
       </c>
       <c r="R18" t="n">
-        <v>6795514</v>
+        <v>6795575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3793,45 +3793,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130058898</v>
+        <v>130058882</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>57019</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440440</v>
+        <v>440465</v>
       </c>
       <c r="R33" t="n">
-        <v>6795865</v>
+        <v>6795787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3864,6 +3872,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blev skrämd och flög iväg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3995,53 +4008,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130058882</v>
+        <v>130058898</v>
       </c>
       <c r="B35" t="n">
-        <v>57019</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440465</v>
+        <v>440440</v>
       </c>
       <c r="R35" t="n">
-        <v>6795787</v>
+        <v>6795865</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,11 +4079,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Blev skrämd och flög iväg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,32 +4417,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130058856</v>
+        <v>130058860</v>
       </c>
       <c r="B39" t="n">
-        <v>57016</v>
+        <v>57985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440406</v>
+        <v>440538</v>
       </c>
       <c r="R39" t="n">
-        <v>6795992</v>
+        <v>6795558</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130058860</v>
+        <v>130058856</v>
       </c>
       <c r="B40" t="n">
-        <v>57985</v>
+        <v>57016</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440538</v>
+        <v>440406</v>
       </c>
       <c r="R40" t="n">
-        <v>6795558</v>
+        <v>6795992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5138,54 +5138,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130058887</v>
+        <v>130058891</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440367</v>
+        <v>440288</v>
       </c>
       <c r="R46" t="n">
-        <v>6796081</v>
+        <v>6796284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5226,7 +5217,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5245,45 +5235,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130058891</v>
+        <v>130058887</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440288</v>
+        <v>440367</v>
       </c>
       <c r="R47" t="n">
-        <v>6796284</v>
+        <v>6796081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5324,6 +5323,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130058876</v>
+        <v>130058847</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440393</v>
+        <v>440505</v>
       </c>
       <c r="R48" t="n">
-        <v>6796027</v>
+        <v>6795644</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,32 +5447,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130058847</v>
+        <v>130058842</v>
       </c>
       <c r="B49" t="n">
-        <v>57016</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440505</v>
+        <v>440461</v>
       </c>
       <c r="R49" t="n">
-        <v>6795644</v>
+        <v>6795771</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130058842</v>
+        <v>130058876</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,16 +5563,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440461</v>
+        <v>440393</v>
       </c>
       <c r="R50" t="n">
-        <v>6795771</v>
+        <v>6796027</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5957,32 +5957,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130058908</v>
+        <v>130058881</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440536</v>
+        <v>440433</v>
       </c>
       <c r="R54" t="n">
-        <v>6795557</v>
+        <v>6795823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,53 +6054,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130058855</v>
+        <v>130058908</v>
       </c>
       <c r="B55" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440292</v>
+        <v>440536</v>
       </c>
       <c r="R55" t="n">
-        <v>6796168</v>
+        <v>6795557</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,7 +6151,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130058848</v>
+        <v>130058855</v>
       </c>
       <c r="B56" t="n">
         <v>57016</v>
@@ -6202,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440460</v>
+        <v>440292</v>
       </c>
       <c r="R56" t="n">
-        <v>6795780</v>
+        <v>6796168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6264,10 +6256,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130058881</v>
+        <v>130058848</v>
       </c>
       <c r="B57" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6275,34 +6267,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440433</v>
+        <v>440460</v>
       </c>
       <c r="R57" t="n">
-        <v>6795823</v>
+        <v>6795780</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130072211</v>
+        <v>130072227</v>
       </c>
       <c r="B70" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7602,42 +7602,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440232</v>
+        <v>440267</v>
       </c>
       <c r="R70" t="n">
-        <v>6796283</v>
+        <v>6796355</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7670,6 +7662,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7696,7 +7693,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130072227</v>
+        <v>130072225</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -7731,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440267</v>
+        <v>440331</v>
       </c>
       <c r="R71" t="n">
-        <v>6796355</v>
+        <v>6796205</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7771,7 +7768,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt inom en radie av 20 m</t>
+          <t>Rikligt inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130072225</v>
+        <v>130072211</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,34 +7806,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440331</v>
+        <v>440232</v>
       </c>
       <c r="R72" t="n">
-        <v>6796205</v>
+        <v>6796283</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7869,11 +7874,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -7182,10 +7182,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130072215</v>
+        <v>130072209</v>
       </c>
       <c r="B66" t="n">
-        <v>56399</v>
+        <v>91749</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,34 +7193,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440306</v>
+        <v>440272</v>
       </c>
       <c r="R66" t="n">
-        <v>6796252</v>
+        <v>6796233</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7261,6 +7268,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7279,10 +7287,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130072209</v>
+        <v>130072215</v>
       </c>
       <c r="B67" t="n">
-        <v>91749</v>
+        <v>56399</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7290,41 +7298,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440272</v>
+        <v>440306</v>
       </c>
       <c r="R67" t="n">
-        <v>6796233</v>
+        <v>6796252</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7365,7 +7366,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59545-2024 artfynd.xlsx
+++ b/artfynd/A 59545-2024 artfynd.xlsx
@@ -7182,10 +7182,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130072209</v>
+        <v>130072215</v>
       </c>
       <c r="B66" t="n">
-        <v>91749</v>
+        <v>56399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,41 +7193,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440272</v>
+        <v>440306</v>
       </c>
       <c r="R66" t="n">
-        <v>6796233</v>
+        <v>6796252</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,7 +7261,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7287,10 +7279,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130072215</v>
+        <v>130072209</v>
       </c>
       <c r="B67" t="n">
-        <v>56399</v>
+        <v>91749</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7298,34 +7290,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440306</v>
+        <v>440272</v>
       </c>
       <c r="R67" t="n">
-        <v>6796252</v>
+        <v>6796233</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7366,6 +7365,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130072227</v>
+        <v>130072211</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7602,34 +7602,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440267</v>
+        <v>440232</v>
       </c>
       <c r="R70" t="n">
-        <v>6796355</v>
+        <v>6796283</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7662,11 +7670,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7693,7 +7696,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130072225</v>
+        <v>130072227</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -7728,10 +7731,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440331</v>
+        <v>440267</v>
       </c>
       <c r="R71" t="n">
-        <v>6796205</v>
+        <v>6796355</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7768,7 +7771,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt inom en radie av 40 m</t>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,10 +7798,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130072211</v>
+        <v>130072225</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,42 +7809,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Södra Snipdalsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440232</v>
+        <v>440331</v>
       </c>
       <c r="R72" t="n">
-        <v>6796283</v>
+        <v>6796205</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,6 +7869,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD72" t="b">
